--- a/embeddings/sandbox/blender/plots/df_f1_donut.xlsx
+++ b/embeddings/sandbox/blender/plots/df_f1_donut.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t xml:space="preserve">es-render-seq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">es-digital-seq_es-render-seq</t>
   </si>
   <si>
     <t xml:space="preserve">britanico_000000</t>
@@ -605,7 +608,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K154"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.28"/>
@@ -640,13 +643,16 @@
       <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="0" t="s">
+        <v>7</v>
+      </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0.0714285714285714</v>
@@ -666,10 +672,13 @@
       <c r="G2" s="0" t="n">
         <v>0.72360248447205</v>
       </c>
+      <c r="H2" s="0" t="n">
+        <v>0.661490683229814</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>0.0571428571428572</v>
@@ -689,10 +698,13 @@
       <c r="G3" s="0" t="n">
         <v>0.495238095238095</v>
       </c>
+      <c r="H3" s="0" t="n">
+        <v>0.461904761904762</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>0.213709677419355</v>
@@ -712,10 +724,13 @@
       <c r="G4" s="0" t="n">
         <v>0.564516129032258</v>
       </c>
+      <c r="H4" s="0" t="n">
+        <v>0.592741935483871</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>0.10655737704918</v>
@@ -735,10 +750,13 @@
       <c r="G5" s="0" t="n">
         <v>0.543715846994536</v>
       </c>
+      <c r="H5" s="0" t="n">
+        <v>0.825136612021858</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>0.344615384615385</v>
@@ -758,10 +776,13 @@
       <c r="G6" s="0" t="n">
         <v>0.750769230769231</v>
       </c>
+      <c r="H6" s="0" t="n">
+        <v>0.756923076923077</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>0</v>
@@ -781,10 +802,13 @@
       <c r="G7" s="0" t="n">
         <v>0.473469387755102</v>
       </c>
+      <c r="H7" s="0" t="n">
+        <v>0.453061224489796</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>0.0338345864661654</v>
@@ -804,10 +828,13 @@
       <c r="G8" s="0" t="n">
         <v>0.714285714285714</v>
       </c>
+      <c r="H8" s="0" t="n">
+        <v>0.473684210526316</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>0.0741935483870968</v>
@@ -827,10 +854,13 @@
       <c r="G9" s="0" t="n">
         <v>0.738709677419355</v>
       </c>
+      <c r="H9" s="0" t="n">
+        <v>0.603225806451613</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>0</v>
@@ -850,10 +880,13 @@
       <c r="G10" s="0" t="n">
         <v>0.672</v>
       </c>
+      <c r="H10" s="0" t="n">
+        <v>0.444</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>0.12890625</v>
@@ -873,10 +906,13 @@
       <c r="G11" s="0" t="n">
         <v>0.64453125</v>
       </c>
+      <c r="H11" s="0" t="n">
+        <v>0.49609375</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>0.171532846715328</v>
@@ -896,10 +932,13 @@
       <c r="G12" s="0" t="n">
         <v>0.697080291970803</v>
       </c>
+      <c r="H12" s="0" t="n">
+        <v>0.324817518248175</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>0</v>
@@ -919,10 +958,13 @@
       <c r="G13" s="0" t="n">
         <v>0.660287081339713</v>
       </c>
+      <c r="H13" s="0" t="n">
+        <v>0.449760765550239</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>0.0358565737051792</v>
@@ -942,10 +984,13 @@
       <c r="G14" s="0" t="n">
         <v>0.462151394422311</v>
       </c>
+      <c r="H14" s="0" t="n">
+        <v>0.326693227091633</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="0" t="n">
         <v>0.271241830065359</v>
@@ -965,10 +1010,13 @@
       <c r="G15" s="0" t="n">
         <v>0.624183006535948</v>
       </c>
+      <c r="H15" s="0" t="n">
+        <v>0.496732026143791</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="0" t="n">
         <v>0</v>
@@ -988,10 +1036,13 @@
       <c r="G16" s="0" t="n">
         <v>0.656652360515021</v>
       </c>
+      <c r="H16" s="0" t="n">
+        <v>0.502145922746781</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="0" t="n">
         <v>0</v>
@@ -1011,10 +1062,13 @@
       <c r="G17" s="0" t="n">
         <v>0.49034749034749</v>
       </c>
+      <c r="H17" s="0" t="n">
+        <v>0.513513513513513</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="0" t="n">
         <v>0</v>
@@ -1034,10 +1088,13 @@
       <c r="G18" s="0" t="n">
         <v>0.904761904761905</v>
       </c>
+      <c r="H18" s="0" t="n">
+        <v>0.885714285714286</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="0" t="n">
         <v>0.041095890410959</v>
@@ -1057,10 +1114,13 @@
       <c r="G19" s="0" t="n">
         <v>0.71689497716895</v>
       </c>
+      <c r="H19" s="0" t="n">
+        <v>0.831050228310502</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="0" t="n">
         <v>0</v>
@@ -1080,10 +1140,13 @@
       <c r="G20" s="0" t="n">
         <v>0.845849802371541</v>
       </c>
+      <c r="H20" s="0" t="n">
+        <v>0.794466403162055</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="0" t="n">
         <v>0</v>
@@ -1103,10 +1166,13 @@
       <c r="G21" s="0" t="n">
         <v>0.931372549019608</v>
       </c>
+      <c r="H21" s="0" t="n">
+        <v>0.901960784313726</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="0" t="n">
         <v>0</v>
@@ -1126,10 +1192,13 @@
       <c r="G22" s="0" t="n">
         <v>0.922330097087379</v>
       </c>
+      <c r="H22" s="0" t="n">
+        <v>0.883495145631068</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="0" t="n">
         <v>0.326829268292683</v>
@@ -1149,10 +1218,13 @@
       <c r="G23" s="0" t="n">
         <v>0.921951219512195</v>
       </c>
+      <c r="H23" s="0" t="n">
+        <v>0.88780487804878</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="0" t="n">
         <v>0.277992277992278</v>
@@ -1172,10 +1244,13 @@
       <c r="G24" s="0" t="n">
         <v>0.845559845559846</v>
       </c>
+      <c r="H24" s="0" t="n">
+        <v>0.849420849420849</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="0" t="n">
         <v>0.424528301886793</v>
@@ -1195,10 +1270,13 @@
       <c r="G25" s="0" t="n">
         <v>0.919811320754717</v>
       </c>
+      <c r="H25" s="0" t="n">
+        <v>0.89622641509434</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="0" t="n">
         <v>0</v>
@@ -1218,10 +1296,13 @@
       <c r="G26" s="0" t="n">
         <v>0.91588785046729</v>
       </c>
+      <c r="H26" s="0" t="n">
+        <v>0.883177570093458</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="0" t="n">
         <v>0</v>
@@ -1241,10 +1322,13 @@
       <c r="G27" s="0" t="n">
         <v>0.841698841698842</v>
       </c>
+      <c r="H27" s="0" t="n">
+        <v>0.845559845559846</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="0" t="n">
         <v>0.173010380622837</v>
@@ -1264,10 +1348,13 @@
       <c r="G28" s="0" t="n">
         <v>0.768166089965398</v>
       </c>
+      <c r="H28" s="0" t="n">
+        <v>0.685121107266436</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="0" t="n">
         <v>0</v>
@@ -1287,10 +1374,13 @@
       <c r="G29" s="0" t="n">
         <v>0.73943661971831</v>
       </c>
+      <c r="H29" s="0" t="n">
+        <v>0.345070422535211</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="0" t="n">
         <v>0.173708920187793</v>
@@ -1310,10 +1400,13 @@
       <c r="G30" s="0" t="n">
         <v>0.915492957746479</v>
       </c>
+      <c r="H30" s="0" t="n">
+        <v>0.751173708920188</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="0" t="n">
         <v>0.0495356037151703</v>
@@ -1333,10 +1426,13 @@
       <c r="G31" s="0" t="n">
         <v>0.801857585139319</v>
       </c>
+      <c r="H31" s="0" t="n">
+        <v>0.643962848297214</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="0" t="n">
         <v>0.031578947368421</v>
@@ -1356,10 +1452,13 @@
       <c r="G32" s="0" t="n">
         <v>0.792982456140351</v>
       </c>
+      <c r="H32" s="0" t="n">
+        <v>0.68421052631579</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="0" t="n">
         <v>0.285234899328859</v>
@@ -1379,10 +1478,13 @@
       <c r="G33" s="0" t="n">
         <v>0.546979865771812</v>
       </c>
+      <c r="H33" s="0" t="n">
+        <v>0.453020134228188</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="0" t="n">
         <v>0.492248062015504</v>
@@ -1402,10 +1504,13 @@
       <c r="G34" s="0" t="n">
         <v>0.844961240310077</v>
       </c>
+      <c r="H34" s="0" t="n">
+        <v>0.883720930232558</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="0" t="n">
         <v>0.454198473282443</v>
@@ -1425,10 +1530,13 @@
       <c r="G35" s="0" t="n">
         <v>0.83587786259542</v>
       </c>
+      <c r="H35" s="0" t="n">
+        <v>0.694656488549618</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="0" t="n">
         <v>0.15</v>
@@ -1448,10 +1556,13 @@
       <c r="G36" s="0" t="n">
         <v>0.775</v>
       </c>
+      <c r="H36" s="0" t="n">
+        <v>0.617857142857143</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="0" t="n">
         <v>0.114285714285714</v>
@@ -1471,10 +1582,13 @@
       <c r="G37" s="0" t="n">
         <v>0.820408163265306</v>
       </c>
+      <c r="H37" s="0" t="n">
+        <v>0.820408163265306</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="0" t="n">
         <v>0</v>
@@ -1494,10 +1608,13 @@
       <c r="G38" s="0" t="n">
         <v>0.795665634674923</v>
       </c>
+      <c r="H38" s="0" t="n">
+        <v>0.662538699690402</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" s="0" t="n">
         <v>0.390243902439024</v>
@@ -1517,10 +1634,13 @@
       <c r="G39" s="0" t="n">
         <v>0.821138211382114</v>
       </c>
+      <c r="H39" s="0" t="n">
+        <v>0.808943089430894</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40" s="0" t="n">
         <v>0.292857142857143</v>
@@ -1540,10 +1660,13 @@
       <c r="G40" s="0" t="n">
         <v>0.75</v>
       </c>
+      <c r="H40" s="0" t="n">
+        <v>0.757142857142857</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="0" t="n">
         <v>0.303405572755418</v>
@@ -1563,10 +1686,13 @@
       <c r="G41" s="0" t="n">
         <v>0.718266253869969</v>
       </c>
+      <c r="H41" s="0" t="n">
+        <v>0.687306501547988</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42" s="0" t="n">
         <v>0.564516129032258</v>
@@ -1586,10 +1712,13 @@
       <c r="G42" s="0" t="n">
         <v>0.845161290322581</v>
       </c>
+      <c r="H42" s="0" t="n">
+        <v>0.761290322580645</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43" s="0" t="n">
         <v>0.445820433436533</v>
@@ -1609,10 +1738,13 @@
       <c r="G43" s="0" t="n">
         <v>0.752321981424149</v>
       </c>
+      <c r="H43" s="0" t="n">
+        <v>0.662538699690402</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" s="0" t="n">
         <v>0</v>
@@ -1632,10 +1764,13 @@
       <c r="G44" s="0" t="n">
         <v>0.775641025641026</v>
       </c>
+      <c r="H44" s="0" t="n">
+        <v>0.580128205128205</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="0" t="n">
         <v>0.434343434343434</v>
@@ -1655,10 +1790,13 @@
       <c r="G45" s="0" t="n">
         <v>0.609427609427609</v>
       </c>
+      <c r="H45" s="0" t="n">
+        <v>0.754208754208754</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46" s="0" t="n">
         <v>0.776041666666667</v>
@@ -1678,10 +1816,13 @@
       <c r="G46" s="0" t="n">
         <v>0.958333333333333</v>
       </c>
+      <c r="H46" s="0" t="n">
+        <v>0.958333333333333</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47" s="0" t="n">
         <v>0.196850393700787</v>
@@ -1701,10 +1842,13 @@
       <c r="G47" s="0" t="n">
         <v>0.81496062992126</v>
       </c>
+      <c r="H47" s="0" t="n">
+        <v>0.874015748031496</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48" s="0" t="n">
         <v>0.164705882352941</v>
@@ -1724,10 +1868,13 @@
       <c r="G48" s="0" t="n">
         <v>0.901960784313726</v>
       </c>
+      <c r="H48" s="0" t="n">
+        <v>0.901960784313726</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49" s="0" t="n">
         <v>0</v>
@@ -1747,10 +1894,13 @@
       <c r="G49" s="0" t="n">
         <v>0.487012987012987</v>
       </c>
+      <c r="H49" s="0" t="n">
+        <v>0.436688311688312</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50" s="0" t="n">
         <v>0.330769230769231</v>
@@ -1770,10 +1920,13 @@
       <c r="G50" s="0" t="n">
         <v>0.811538461538462</v>
       </c>
+      <c r="H50" s="0" t="n">
+        <v>0.873076923076923</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51" s="0" t="n">
         <v>0</v>
@@ -1793,10 +1946,13 @@
       <c r="G51" s="0" t="n">
         <v>0.296052631578947</v>
       </c>
+      <c r="H51" s="0" t="n">
+        <v>0.598684210526316</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52" s="0" t="n">
         <v>0.189723320158103</v>
@@ -1816,10 +1972,13 @@
       <c r="G52" s="0" t="n">
         <v>0.909090909090909</v>
       </c>
+      <c r="H52" s="0" t="n">
+        <v>0.909090909090909</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53" s="0" t="n">
         <v>0</v>
@@ -1839,10 +1998,13 @@
       <c r="G53" s="0" t="n">
         <v>0.478190630048465</v>
       </c>
+      <c r="H53" s="0" t="n">
+        <v>0.584814216478191</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54" s="0" t="n">
         <v>0</v>
@@ -1862,10 +2024,13 @@
       <c r="G54" s="0" t="n">
         <v>0.875</v>
       </c>
+      <c r="H54" s="0" t="n">
+        <v>0.776515151515152</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55" s="0" t="n">
         <v>0.234248788368336</v>
@@ -1885,10 +2050,13 @@
       <c r="G55" s="0" t="n">
         <v>0.35702746365105</v>
       </c>
+      <c r="H55" s="0" t="n">
+        <v>0.294022617124394</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B56" s="0" t="n">
         <v>0.305220883534137</v>
@@ -1908,10 +2076,13 @@
       <c r="G56" s="0" t="n">
         <v>0.907630522088353</v>
       </c>
+      <c r="H56" s="0" t="n">
+        <v>0.907630522088353</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B57" s="0" t="n">
         <v>0.269607843137255</v>
@@ -1931,10 +2102,13 @@
       <c r="G57" s="0" t="n">
         <v>0.51797385620915</v>
       </c>
+      <c r="H57" s="0" t="n">
+        <v>0.637254901960784</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>0.168831168831169</v>
@@ -1954,10 +2128,13 @@
       <c r="G58" s="0" t="n">
         <v>0.917748917748918</v>
       </c>
+      <c r="H58" s="0" t="n">
+        <v>0.917748917748918</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>0.300787401574803</v>
@@ -1977,10 +2154,13 @@
       <c r="G59" s="0" t="n">
         <v>0.322834645669291</v>
       </c>
+      <c r="H59" s="0" t="n">
+        <v>0.659842519685039</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>0.265527950310559</v>
@@ -2000,10 +2180,13 @@
       <c r="G60" s="0" t="n">
         <v>0.56832298136646</v>
       </c>
+      <c r="H60" s="0" t="n">
+        <v>0.518633540372671</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>0.142241379310345</v>
@@ -2023,10 +2206,13 @@
       <c r="G61" s="0" t="n">
         <v>0.939655172413793</v>
       </c>
+      <c r="H61" s="0" t="n">
+        <v>0.844827586206896</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>0.212355212355212</v>
@@ -2046,10 +2232,13 @@
       <c r="G62" s="0" t="n">
         <v>0.806949806949807</v>
       </c>
+      <c r="H62" s="0" t="n">
+        <v>0.872586872586873</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>0.160377358490566</v>
@@ -2069,10 +2258,13 @@
       <c r="G63" s="0" t="n">
         <v>0.360062893081761</v>
       </c>
+      <c r="H63" s="0" t="n">
+        <v>0.572327044025157</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>0</v>
@@ -2092,10 +2284,13 @@
       <c r="G64" s="0" t="n">
         <v>0.626050420168067</v>
       </c>
+      <c r="H64" s="0" t="n">
+        <v>0.626050420168067</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>0.170686456400742</v>
@@ -2115,10 +2310,13 @@
       <c r="G65" s="0" t="n">
         <v>0.285714285714286</v>
       </c>
+      <c r="H65" s="0" t="n">
+        <v>0.573283858998145</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>0.120629370629371</v>
@@ -2138,10 +2336,13 @@
       <c r="G66" s="0" t="n">
         <v>0.428321678321678</v>
       </c>
+      <c r="H66" s="0" t="n">
+        <v>0.611888111888112</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B67" s="0" t="n">
         <v>0.103448275862069</v>
@@ -2161,10 +2362,13 @@
       <c r="G67" s="0" t="n">
         <v>0.719211822660099</v>
       </c>
+      <c r="H67" s="0" t="n">
+        <v>0.719211822660099</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B68" s="0" t="n">
         <v>0.45136186770428</v>
@@ -2184,10 +2388,13 @@
       <c r="G68" s="0" t="n">
         <v>0.785992217898833</v>
       </c>
+      <c r="H68" s="0" t="n">
+        <v>0.793774319066148</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>0</v>
@@ -2207,10 +2414,13 @@
       <c r="G69" s="0" t="n">
         <v>0.572898799313894</v>
       </c>
+      <c r="H69" s="0" t="n">
+        <v>0.672384219554031</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>0.163025210084034</v>
@@ -2230,10 +2440,13 @@
       <c r="G70" s="0" t="n">
         <v>0.563025210084034</v>
       </c>
+      <c r="H70" s="0" t="n">
+        <v>0.326050420168067</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>0.375527426160337</v>
@@ -2253,10 +2466,13 @@
       <c r="G71" s="0" t="n">
         <v>0.822784810126582</v>
       </c>
+      <c r="H71" s="0" t="n">
+        <v>0.822784810126582</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B72" s="0" t="n">
         <v>0</v>
@@ -2276,10 +2492,13 @@
       <c r="G72" s="0" t="n">
         <v>0.442404006677796</v>
       </c>
+      <c r="H72" s="0" t="n">
+        <v>0.629382303839733</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B73" s="0" t="n">
         <v>0</v>
@@ -2299,10 +2518,13 @@
       <c r="G73" s="0" t="n">
         <v>0.636734693877551</v>
       </c>
+      <c r="H73" s="0" t="n">
+        <v>0.636734693877551</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>0.0141843971631206</v>
@@ -2322,10 +2544,13 @@
       <c r="G74" s="0" t="n">
         <v>0.696808510638298</v>
       </c>
+      <c r="H74" s="0" t="n">
+        <v>0.572695035460993</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>0.344398340248963</v>
@@ -2345,10 +2570,13 @@
       <c r="G75" s="0" t="n">
         <v>0.630705394190871</v>
       </c>
+      <c r="H75" s="0" t="n">
+        <v>0.630705394190871</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>0</v>
@@ -2368,10 +2596,13 @@
       <c r="G76" s="0" t="n">
         <v>0.543918918918919</v>
       </c>
+      <c r="H76" s="0" t="n">
+        <v>0.564189189189189</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B77" s="0" t="n">
         <v>0</v>
@@ -2391,10 +2622,13 @@
       <c r="G77" s="0" t="n">
         <v>0.326848249027237</v>
       </c>
+      <c r="H77" s="0" t="n">
+        <v>0.474708171206226</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B78" s="0" t="n">
         <v>0</v>
@@ -2414,10 +2648,13 @@
       <c r="G78" s="0" t="n">
         <v>0.491921005385996</v>
       </c>
+      <c r="H78" s="0" t="n">
+        <v>0.721723518850987</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B79" s="0" t="n">
         <v>0</v>
@@ -2437,10 +2674,13 @@
       <c r="G79" s="0" t="n">
         <v>0.838297872340426</v>
       </c>
+      <c r="H79" s="0" t="n">
+        <v>0.625531914893617</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B80" s="0" t="n">
         <v>0</v>
@@ -2460,10 +2700,13 @@
       <c r="G80" s="0" t="n">
         <v>0.868544600938967</v>
       </c>
+      <c r="H80" s="0" t="n">
+        <v>0.619718309859155</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>0.292553191489362</v>
@@ -2483,10 +2726,13 @@
       <c r="G81" s="0" t="n">
         <v>0.585106382978723</v>
       </c>
+      <c r="H81" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B82" s="0" t="n">
         <v>0.0833333333333334</v>
@@ -2506,10 +2752,13 @@
       <c r="G82" s="0" t="n">
         <v>0.541666666666667</v>
       </c>
+      <c r="H82" s="0" t="n">
+        <v>0.0879629629629629</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B83" s="0" t="n">
         <v>0</v>
@@ -2529,10 +2778,13 @@
       <c r="G83" s="0" t="n">
         <v>0.261682242990654</v>
       </c>
+      <c r="H83" s="0" t="n">
+        <v>0.350467289719626</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>0</v>
@@ -2552,10 +2804,13 @@
       <c r="G84" s="0" t="n">
         <v>0.991452991452992</v>
       </c>
+      <c r="H84" s="0" t="n">
+        <v>0.0683760683760684</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>0.0630630630630631</v>
@@ -2575,10 +2830,13 @@
       <c r="G85" s="0" t="n">
         <v>0.747747747747748</v>
       </c>
+      <c r="H85" s="0" t="n">
+        <v>0.40990990990991</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="0" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>0</v>
@@ -2598,10 +2856,13 @@
       <c r="G86" s="0" t="n">
         <v>0.852216748768473</v>
       </c>
+      <c r="H86" s="0" t="n">
+        <v>0.921182266009852</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B87" s="0" t="n">
         <v>0</v>
@@ -2621,10 +2882,13 @@
       <c r="G87" s="0" t="n">
         <v>0.61437908496732</v>
       </c>
+      <c r="H87" s="0" t="n">
+        <v>0.627450980392157</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B88" s="0" t="n">
         <v>0</v>
@@ -2644,10 +2908,13 @@
       <c r="G88" s="0" t="n">
         <v>0.664150943396226</v>
       </c>
+      <c r="H88" s="0" t="n">
+        <v>0.581132075471698</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B89" s="0" t="n">
         <v>0</v>
@@ -2667,10 +2934,13 @@
       <c r="G89" s="0" t="n">
         <v>0.829896907216495</v>
       </c>
+      <c r="H89" s="0" t="n">
+        <v>0.0257731958762887</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B90" s="0" t="n">
         <v>0.437908496732026</v>
@@ -2690,10 +2960,13 @@
       <c r="G90" s="0" t="n">
         <v>0.702614379084967</v>
       </c>
+      <c r="H90" s="0" t="n">
+        <v>0.800653594771242</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B91" s="0" t="n">
         <v>0.0511811023622047</v>
@@ -2713,10 +2986,13 @@
       <c r="G91" s="0" t="n">
         <v>0.724409448818898</v>
       </c>
+      <c r="H91" s="0" t="n">
+        <v>0.661417322834646</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B92" s="0" t="n">
         <v>0.0598290598290598</v>
@@ -2736,10 +3012,13 @@
       <c r="G92" s="0" t="n">
         <v>0.82051282051282</v>
       </c>
+      <c r="H92" s="0" t="n">
+        <v>0.773504273504274</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B93" s="0" t="n">
         <v>0</v>
@@ -2759,10 +3038,13 @@
       <c r="G93" s="0" t="n">
         <v>0.61965811965812</v>
       </c>
+      <c r="H93" s="0" t="n">
+        <v>0.277777777777778</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B94" s="0" t="n">
         <v>0</v>
@@ -2782,10 +3064,13 @@
       <c r="G94" s="0" t="n">
         <v>0.940217391304348</v>
       </c>
+      <c r="H94" s="0" t="n">
+        <v>0.239130434782609</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B95" s="0" t="n">
         <v>0</v>
@@ -2805,10 +3090,13 @@
       <c r="G95" s="0" t="n">
         <v>0.866425992779783</v>
       </c>
+      <c r="H95" s="0" t="n">
+        <v>0.837545126353791</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B96" s="0" t="n">
         <v>0</v>
@@ -2828,10 +3116,13 @@
       <c r="G96" s="0" t="n">
         <v>0.828193832599119</v>
       </c>
+      <c r="H96" s="0" t="n">
+        <v>0.881057268722467</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B97" s="0" t="n">
         <v>0</v>
@@ -2851,10 +3142,13 @@
       <c r="G97" s="0" t="n">
         <v>0.868913857677903</v>
       </c>
+      <c r="H97" s="0" t="n">
+        <v>0.426966292134831</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B98" s="0" t="n">
         <v>0</v>
@@ -2874,10 +3168,13 @@
       <c r="G98" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="H98" s="0" t="n">
+        <v>0.846491228070175</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B99" s="0" t="n">
         <v>0</v>
@@ -2897,10 +3194,13 @@
       <c r="G99" s="0" t="n">
         <v>0.782771535580524</v>
       </c>
+      <c r="H99" s="0" t="n">
+        <v>0.730337078651685</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>0</v>
@@ -2920,10 +3220,13 @@
       <c r="G100" s="0" t="n">
         <v>0.845588235294118</v>
       </c>
+      <c r="H100" s="0" t="n">
+        <v>0.426470588235294</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B101" s="0" t="n">
         <v>0.124031007751938</v>
@@ -2943,10 +3246,13 @@
       <c r="G101" s="0" t="n">
         <v>0.767441860465116</v>
       </c>
+      <c r="H101" s="0" t="n">
+        <v>0.775193798449612</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B102" s="0" t="n">
         <v>0.0674603174603174</v>
@@ -2966,10 +3272,13 @@
       <c r="G102" s="0" t="n">
         <v>0.825396825396825</v>
       </c>
+      <c r="H102" s="0" t="n">
+        <v>0.214285714285714</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B103" s="0" t="n">
         <v>0</v>
@@ -2989,10 +3298,13 @@
       <c r="G103" s="0" t="n">
         <v>0.824902723735409</v>
       </c>
+      <c r="H103" s="0" t="n">
+        <v>0.626459143968872</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>0</v>
@@ -3012,10 +3324,13 @@
       <c r="G104" s="0" t="n">
         <v>0.809128630705394</v>
       </c>
+      <c r="H104" s="0" t="n">
+        <v>0.730290456431535</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B105" s="0" t="n">
         <v>0</v>
@@ -3035,10 +3350,13 @@
       <c r="G105" s="0" t="n">
         <v>0.630188679245283</v>
       </c>
+      <c r="H105" s="0" t="n">
+        <v>0.728301886792453</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B106" s="0" t="n">
         <v>0.650793650793651</v>
@@ -3058,10 +3376,13 @@
       <c r="G106" s="0" t="n">
         <v>0.869047619047619</v>
       </c>
+      <c r="H106" s="0" t="n">
+        <v>0.797619047619048</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B107" s="0" t="n">
         <v>0</v>
@@ -3081,10 +3402,13 @@
       <c r="G107" s="0" t="n">
         <v>0.921296296296296</v>
       </c>
+      <c r="H107" s="0" t="n">
+        <v>0.162037037037037</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B108" s="0" t="n">
         <v>0.00190476190476185</v>
@@ -3104,10 +3428,13 @@
       <c r="G108" s="0" t="n">
         <v>0.457142857142857</v>
       </c>
+      <c r="H108" s="0" t="n">
+        <v>0.611428571428571</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B109" s="0" t="n">
         <v>0.0457875457875457</v>
@@ -3127,10 +3454,13 @@
       <c r="G109" s="0" t="n">
         <v>0.283882783882784</v>
       </c>
+      <c r="H109" s="0" t="n">
+        <v>0.582417582417582</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B110" s="0" t="n">
         <v>0.180769230769231</v>
@@ -3150,10 +3480,13 @@
       <c r="G110" s="0" t="n">
         <v>0.348076923076923</v>
       </c>
+      <c r="H110" s="0" t="n">
+        <v>0.565384615384615</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B111" s="0" t="n">
         <v>0.142592592592593</v>
@@ -3173,10 +3506,13 @@
       <c r="G111" s="0" t="n">
         <v>0.257407407407407</v>
       </c>
+      <c r="H111" s="0" t="n">
+        <v>0.257407407407407</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B112" s="0" t="n">
         <v>0.105166051660517</v>
@@ -3196,10 +3532,13 @@
       <c r="G112" s="0" t="n">
         <v>0.380073800738007</v>
       </c>
+      <c r="H112" s="0" t="n">
+        <v>0.446494464944649</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B113" s="0" t="n">
         <v>0.301470588235294</v>
@@ -3219,10 +3558,13 @@
       <c r="G113" s="0" t="n">
         <v>0.492647058823529</v>
       </c>
+      <c r="H113" s="0" t="n">
+        <v>0.481617647058823</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B114" s="0" t="n">
         <v>0.234545454545454</v>
@@ -3242,10 +3584,13 @@
       <c r="G114" s="0" t="n">
         <v>0.485454545454545</v>
       </c>
+      <c r="H114" s="0" t="n">
+        <v>0.350909090909091</v>
+      </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B115" s="0" t="n">
         <v>0.142857142857143</v>
@@ -3265,10 +3610,13 @@
       <c r="G115" s="0" t="n">
         <v>0.332096474953618</v>
       </c>
+      <c r="H115" s="0" t="n">
+        <v>0.38961038961039</v>
+      </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B116" s="0" t="n">
         <v>0.0390334572490706</v>
@@ -3288,10 +3636,13 @@
       <c r="G116" s="0" t="n">
         <v>0.429368029739777</v>
       </c>
+      <c r="H116" s="0" t="n">
+        <v>0.611524163568773</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B117" s="0" t="n">
         <v>0</v>
@@ -3311,10 +3662,13 @@
       <c r="G117" s="0" t="n">
         <v>0.323583180987203</v>
       </c>
+      <c r="H117" s="0" t="n">
+        <v>0.431444241316271</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B118" s="0" t="n">
         <v>0.258064516129032</v>
@@ -3334,10 +3688,13 @@
       <c r="G118" s="0" t="n">
         <v>0.358633776091082</v>
       </c>
+      <c r="H118" s="0" t="n">
+        <v>0.335863377609108</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B119" s="0" t="n">
         <v>0.100569259962049</v>
@@ -3357,10 +3714,13 @@
       <c r="G119" s="0" t="n">
         <v>0.28842504743833</v>
       </c>
+      <c r="H119" s="0" t="n">
+        <v>0.332068311195446</v>
+      </c>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B120" s="0" t="n">
         <v>0.0601503759398496</v>
@@ -3380,10 +3740,13 @@
       <c r="G120" s="0" t="n">
         <v>0.171052631578947</v>
       </c>
+      <c r="H120" s="0" t="n">
+        <v>0.343984962406015</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B121" s="0" t="n">
         <v>0.329588014981273</v>
@@ -3403,10 +3766,13 @@
       <c r="G121" s="0" t="n">
         <v>0.741573033707865</v>
       </c>
+      <c r="H121" s="0" t="n">
+        <v>0.820224719101124</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B122" s="0" t="n">
         <v>0.379746835443038</v>
@@ -3426,10 +3792,13 @@
       <c r="G122" s="0" t="n">
         <v>0.877637130801688</v>
       </c>
+      <c r="H122" s="0" t="n">
+        <v>0.877637130801688</v>
+      </c>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B123" s="0" t="n">
         <v>0.211155378486056</v>
@@ -3449,10 +3818,13 @@
       <c r="G123" s="0" t="n">
         <v>0.832669322709163</v>
       </c>
+      <c r="H123" s="0" t="n">
+        <v>0.872509960159363</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B124" s="0" t="n">
         <v>0.272727272727273</v>
@@ -3472,10 +3844,13 @@
       <c r="G124" s="0" t="n">
         <v>0.859848484848485</v>
       </c>
+      <c r="H124" s="0" t="n">
+        <v>0.829545454545455</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>0.104347826086956</v>
@@ -3495,10 +3870,13 @@
       <c r="G125" s="0" t="n">
         <v>0.88695652173913</v>
       </c>
+      <c r="H125" s="0" t="n">
+        <v>0.908695652173913</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B126" s="0" t="n">
         <v>0.298507462686567</v>
@@ -3518,10 +3896,13 @@
       <c r="G126" s="0" t="n">
         <v>0.83955223880597</v>
       </c>
+      <c r="H126" s="0" t="n">
+        <v>0.779850746268657</v>
+      </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B127" s="0" t="n">
         <v>0.39647577092511</v>
@@ -3541,10 +3922,13 @@
       <c r="G127" s="0" t="n">
         <v>0.845814977973568</v>
       </c>
+      <c r="H127" s="0" t="n">
+        <v>0.740088105726872</v>
+      </c>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B128" s="0" t="n">
         <v>0.548076923076923</v>
@@ -3564,10 +3948,13 @@
       <c r="G128" s="0" t="n">
         <v>0.889423076923077</v>
       </c>
+      <c r="H128" s="0" t="n">
+        <v>0.841346153846154</v>
+      </c>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B129" s="0" t="n">
         <v>0.253164556962025</v>
@@ -3587,10 +3974,13 @@
       <c r="G129" s="0" t="n">
         <v>0.843881856540084</v>
       </c>
+      <c r="H129" s="0" t="n">
+        <v>0.881856540084388</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B130" s="0" t="n">
         <v>0.273408239700375</v>
@@ -3610,10 +4000,13 @@
       <c r="G130" s="0" t="n">
         <v>0.857677902621723</v>
       </c>
+      <c r="H130" s="0" t="n">
+        <v>0.805243445692884</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>0.392344497607656</v>
@@ -3633,10 +4026,13 @@
       <c r="G131" s="0" t="n">
         <v>0.870813397129187</v>
       </c>
+      <c r="H131" s="0" t="n">
+        <v>0.837320574162679</v>
+      </c>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B132" s="0" t="n">
         <v>0.230769230769231</v>
@@ -3656,10 +4052,13 @@
       <c r="G132" s="0" t="n">
         <v>0.448351648351648</v>
       </c>
+      <c r="H132" s="0" t="n">
+        <v>0.443956043956044</v>
+      </c>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B133" s="0" t="n">
         <v>0.290909090909091</v>
@@ -3679,10 +4078,13 @@
       <c r="G133" s="0" t="n">
         <v>0.843636363636364</v>
       </c>
+      <c r="H133" s="0" t="n">
+        <v>0.803636363636364</v>
+      </c>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B134" s="0" t="n">
         <v>0.314159292035398</v>
@@ -3702,10 +4104,13 @@
       <c r="G134" s="0" t="n">
         <v>0.933628318584071</v>
       </c>
+      <c r="H134" s="0" t="n">
+        <v>0.933628318584071</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B135" s="0" t="n">
         <v>0.0566801619433198</v>
@@ -3725,10 +4130,13 @@
       <c r="G135" s="0" t="n">
         <v>0.854251012145749</v>
       </c>
+      <c r="H135" s="0" t="n">
+        <v>0.825910931174089</v>
+      </c>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>0.255813953488372</v>
@@ -3748,10 +4156,13 @@
       <c r="G136" s="0" t="n">
         <v>0.852713178294574</v>
       </c>
+      <c r="H136" s="0" t="n">
+        <v>0.868217054263566</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B137" s="0" t="n">
         <v>0.0437956204379562</v>
@@ -3771,10 +4182,13 @@
       <c r="G137" s="0" t="n">
         <v>0.875912408759124</v>
       </c>
+      <c r="H137" s="0" t="n">
+        <v>0.68978102189781</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B138" s="0" t="n">
         <v>0</v>
@@ -3794,10 +4208,13 @@
       <c r="G138" s="0" t="n">
         <v>0.924302788844621</v>
       </c>
+      <c r="H138" s="0" t="n">
+        <v>0.844621513944223</v>
+      </c>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B139" s="0" t="n">
         <v>0</v>
@@ -3817,10 +4234,13 @@
       <c r="G139" s="0" t="n">
         <v>0.939130434782609</v>
       </c>
+      <c r="H139" s="0" t="n">
+        <v>0.773913043478261</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B140" s="0" t="n">
         <v>0</v>
@@ -3840,10 +4260,13 @@
       <c r="G140" s="0" t="n">
         <v>0.841911764705882</v>
       </c>
+      <c r="H140" s="0" t="n">
+        <v>0.867647058823529</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B141" s="0" t="n">
         <v>0</v>
@@ -3863,10 +4286,13 @@
       <c r="G141" s="0" t="n">
         <v>0.878980891719745</v>
       </c>
+      <c r="H141" s="0" t="n">
+        <v>0.847133757961784</v>
+      </c>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B142" s="0" t="n">
         <v>0.12624584717608</v>
@@ -3886,10 +4312,13 @@
       <c r="G142" s="0" t="n">
         <v>0.877076411960133</v>
       </c>
+      <c r="H142" s="0" t="n">
+        <v>0.903654485049834</v>
+      </c>
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B143" s="0" t="n">
         <v>0</v>
@@ -3909,10 +4338,13 @@
       <c r="G143" s="0" t="n">
         <v>0.963636363636364</v>
       </c>
+      <c r="H143" s="0" t="n">
+        <v>0.754545454545455</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B144" s="0" t="n">
         <v>0</v>
@@ -3932,10 +4364,13 @@
       <c r="G144" s="0" t="n">
         <v>0.848360655737705</v>
       </c>
+      <c r="H144" s="0" t="n">
+        <v>0.872950819672131</v>
+      </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B145" s="0" t="n">
         <v>0</v>
@@ -3955,10 +4390,13 @@
       <c r="G145" s="0" t="n">
         <v>0.860557768924303</v>
       </c>
+      <c r="H145" s="0" t="n">
+        <v>0.904382470119522</v>
+      </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B146" s="0" t="n">
         <v>0</v>
@@ -3978,10 +4416,13 @@
       <c r="G146" s="0" t="n">
         <v>0.751908396946565</v>
       </c>
+      <c r="H146" s="0" t="n">
+        <v>0.881679389312977</v>
+      </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B147" s="0" t="n">
         <v>0</v>
@@ -4001,10 +4442,13 @@
       <c r="G147" s="0" t="n">
         <v>0.629139072847682</v>
       </c>
+      <c r="H147" s="0" t="n">
+        <v>0.645695364238411</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B148" s="0" t="n">
         <v>0</v>
@@ -4024,10 +4468,13 @@
       <c r="G148" s="0" t="n">
         <v>0.78021978021978</v>
       </c>
+      <c r="H148" s="0" t="n">
+        <v>0.864468864468864</v>
+      </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B149" s="0" t="n">
         <v>0</v>
@@ -4047,10 +4494,13 @@
       <c r="G149" s="0" t="n">
         <v>0.91747572815534</v>
       </c>
+      <c r="H149" s="0" t="n">
+        <v>0.849514563106796</v>
+      </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B150" s="0" t="n">
         <v>0</v>
@@ -4070,10 +4520,13 @@
       <c r="G150" s="0" t="n">
         <v>0.787545787545788</v>
       </c>
+      <c r="H150" s="0" t="n">
+        <v>0.736263736263736</v>
+      </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B151" s="0" t="n">
         <v>0</v>
@@ -4093,10 +4546,13 @@
       <c r="G151" s="0" t="n">
         <v>0.865771812080537</v>
       </c>
+      <c r="H151" s="0" t="n">
+        <v>0.875838926174497</v>
+      </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B152" s="0" t="n">
         <v>0</v>
@@ -4116,10 +4572,13 @@
       <c r="G152" s="0" t="n">
         <v>0.816176470588235</v>
       </c>
+      <c r="H152" s="0" t="n">
+        <v>0.875</v>
+      </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B153" s="0" t="n">
         <v>0</v>
@@ -4139,11 +4598,44 @@
       <c r="G153" s="0" t="n">
         <v>0.869706840390879</v>
       </c>
+      <c r="H153" s="0" t="n">
+        <v>0.837133550488599</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B154" s="0" t="n">
+        <f aca="false">AVERAGE(B2:B153)</f>
+        <v>0.135631466164151</v>
+      </c>
+      <c r="C154" s="0" t="n">
+        <f aca="false">AVERAGE(C2:C153)</f>
+        <v>0.0665301001125611</v>
+      </c>
+      <c r="D154" s="0" t="n">
+        <f aca="false">AVERAGE(D2:D153)</f>
+        <v>0.338581449747222</v>
+      </c>
+      <c r="E154" s="0" t="n">
+        <f aca="false">AVERAGE(E2:E153)</f>
+        <v>0.562635261348711</v>
+      </c>
+      <c r="F154" s="0" t="n">
+        <f aca="false">AVERAGE(F2:F153)</f>
+        <v>0.706181337165451</v>
+      </c>
+      <c r="G154" s="0" t="n">
+        <f aca="false">AVERAGE(G2:G153)</f>
+        <v>0.704908329891812</v>
+      </c>
+      <c r="H154" s="0" t="n">
+        <f aca="false">AVERAGE(H2:H153)</f>
+        <v>0.663781641602204</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
